--- a/Informes/Informe_Palestino_vs_UVC_2026-09-08.xlsx
+++ b/Informes/Informe_Palestino_vs_UVC_2026-09-08.xlsx
@@ -5359,28 +5359,28 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -5390,28 +5390,28 @@
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>0</v>
@@ -5433,16 +5433,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -5458,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>0</v>
@@ -5467,13 +5467,13 @@
         <v>0</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C30" s="11" t="n">
         <v>0</v>
@@ -5498,13 +5498,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -5551,22 +5551,22 @@
         <v>0</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -5588,16 +5588,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>0</v>
@@ -5622,13 +5622,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -5638,28 +5638,28 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36"/>
